--- a/src/test/resources/excel/DatosPruebaWeb.xlsx
+++ b/src/test/resources/excel/DatosPruebaWeb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHON\Documents\GitHub\Bon-Bonite\src\test\resources\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automatizacion\Practivas Automatización Web\PruebaTenicaAutomatizacionWeb\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D816D20-B92D-4A8E-B1F6-C80AC5764999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F4CC46-55F4-421D-852F-8447F558016A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Registro" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>Correo electronico</t>
   </si>
@@ -71,7 +71,7 @@
     <t>Zapatos</t>
   </si>
   <si>
-    <t>Sandalia de plataforma en cuero duna</t>
+    <t>Baleta en cuero borgoña</t>
   </si>
   <si>
     <t>Usuario</t>
@@ -89,16 +89,22 @@
     <t>Outlet</t>
   </si>
   <si>
-    <t>Cartera en cuero chantilly</t>
-  </si>
-  <si>
-    <t>Cinturón doble faz en cuero pelicano por azul profundo</t>
+    <t>Manos libres en cuero luna</t>
+  </si>
+  <si>
+    <t>Cinturón en cuero negro</t>
   </si>
   <si>
     <t>Billetera en cuero rojo escarlata</t>
   </si>
   <si>
-    <t>Tenis sin cordón en textil color lavanda</t>
+    <t>Baleta en cuero con glitter color negro ónix</t>
+  </si>
+  <si>
+    <t>Camil0</t>
+  </si>
+  <si>
+    <t>Camila.pruebas02@pruebas.com</t>
   </si>
 </sst>
 </file>
@@ -443,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
@@ -493,9 +499,30 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>342314544</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{D8F1314E-68CA-4FA3-8A3C-8F3643DDDAD5}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{11AFE858-9DF1-477A-B81D-4043E9AD8A47}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -620,6 +647,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF40919-2ECE-4A74-BA17-F3DCA045FA3A}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
